--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487963_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487963_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3066</v>
+        <v>3.4217</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9841</v>
+        <v>5.4487</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3225</v>
+        <v>-2.0271</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2142</v>
+        <v>2.2854</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5566</v>
+        <v>0.2136</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3424</v>
+        <v>2.0719</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9787</v>
+        <v>5.1984</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2516</v>
+        <v>1.944</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7271</v>
+        <v>3.2544</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1928</v>
+        <v>-2.9129</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8081</v>
+        <v>-1.7304</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3847</v>
+        <v>-1.1825</v>
       </c>
       <c r="P2" t="n">
+        <v>1.5858</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-0.1982</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1.9822</v>
       </c>
       <c r="R2" t="n">
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7785</v>
+        <v>-1.3196</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7806</v>
+        <v>-0.6881</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9979</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9405</v>
+        <v>0.8701</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X2" t="n">
         <v>-0.2666</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7481</v>
+        <v>1.2513</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7751</v>
+        <v>1.5184</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0271</v>
+        <v>-0.2671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2854</v>
+        <v>-0.2142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2136</v>
+        <v>-0.5566</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0719</v>
+        <v>0.3424</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1984</v>
+        <v>1.9787</v>
       </c>
       <c r="K3" t="n">
-        <v>1.944</v>
+        <v>1.2516</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2544</v>
+        <v>0.7271</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9129</v>
+        <v>-2.1928</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7304</v>
+        <v>-1.8081</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1825</v>
+        <v>-0.3847</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5858</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9933</v>
+        <v>0.7232</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3617</v>
+        <v>0.3149</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6316000000000001</v>
+        <v>0.4083</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8701</v>
+        <v>0.9405</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>J. PÁEZ ÁVILA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6031</v>
+        <v>0.6027</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2885</v>
+        <v>0.6027</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6854</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9792</v>
+        <v>0.6027</v>
       </c>
       <c r="H4" t="n">
-        <v>1.501</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4782</v>
+        <v>0.6027</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5535</v>
+        <v>0.6027</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9419999999999999</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6115</v>
+        <v>0.6027</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5743</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1333</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.5591</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.9467</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2357</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7343</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4986</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PÁEZ ÁVILA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6027</v>
+        <v>0.3555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6027</v>
+        <v>1.5717</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.2162</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6027</v>
+        <v>-0.8219</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1.6944</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6027</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6027</v>
+        <v>1.8854</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6027</v>
+        <v>1.7834</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.7072</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.7964</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.9109</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1.1398</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.6486</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.4912</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5042</v>
+        <v>0.2747</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7962</v>
+        <v>0.9039</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3004</v>
+        <v>-0.6292</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8219</v>
+        <v>1.9792</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6944</v>
+        <v>1.501</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.4782</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8854</v>
+        <v>3.5535</v>
       </c>
       <c r="K6" t="n">
-        <v>0.102</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7834</v>
+        <v>2.6115</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7072</v>
+        <v>-1.5743</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7964</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9109</v>
+        <v>-2.1333</v>
       </c>
       <c r="P6" t="n">
-        <v>1.784</v>
+        <v>-4.5591</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1982</v>
+        <v>-5.9467</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9995</v>
+        <v>-0.0927</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4241</v>
+        <v>0.3497</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5754</v>
+        <v>-0.4425</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5331</v>
+        <v>2.9474</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5331</v>
+        <v>2.9474</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.544</v>
+        <v>-0.5834</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1295</v>
+        <v>1.09</v>
       </c>
       <c r="F7" t="n">
         <v>-1.6735</v>
@@ -1000,10 +1000,10 @@
         <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3655</v>
+        <v>-1.405</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5578</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U7" t="n">
         <v>-0.8077</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.648</v>
+        <v>-1.2004</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4788</v>
+        <v>-0.4564</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1269</v>
+        <v>-0.744</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8407</v>
+        <v>0.4868</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0498</v>
+        <v>-0.309</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7909</v>
+        <v>0.7958</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3421</v>
+        <v>2.604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1412</v>
+        <v>1.1576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2009</v>
+        <v>1.4464</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1828</v>
+        <v>-2.1172</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.191</v>
+        <v>-1.4666</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9918</v>
+        <v>-0.6506</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1893</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2104</v>
+        <v>-0.2312</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3349</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.1245</v>
+        <v>-0.1442</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0903</v>
+        <v>-1.6443</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3201</v>
+        <v>-2.0144</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2298</v>
+        <v>0.3702</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9232</v>
@@ -1156,13 +1156,13 @@
         <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.167</v>
+        <v>0.279</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1248</v>
+        <v>0.1808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0422</v>
+        <v>0.0982</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4033</v>
+        <v>-1.9576</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2943</v>
+        <v>0.2017</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.109</v>
+        <v>-2.1593</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4868</v>
+        <v>-1.0194</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.309</v>
+        <v>0.2795</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7958</v>
+        <v>-1.2989</v>
       </c>
       <c r="J10" t="n">
-        <v>2.604</v>
+        <v>1.3075</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1576</v>
+        <v>1.4124</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4464</v>
+        <v>-0.105</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1172</v>
+        <v>-2.3269</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4666</v>
+        <v>-1.1329</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6506</v>
+        <v>-1.1939</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4341</v>
+        <v>-0.3258</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.1146</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5092</v>
+        <v>-0.2112</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6479</v>
+        <v>-2.701</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4324</v>
+        <v>-0.4463</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2155</v>
+        <v>-2.2547</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0194</v>
+        <v>-2.3896</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2795</v>
+        <v>-1.2092</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2989</v>
+        <v>-1.1804</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3075</v>
+        <v>-0.451</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4124</v>
+        <v>0.0674</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.105</v>
+        <v>-0.5184</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3269</v>
+        <v>-1.9386</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1329</v>
+        <v>-1.2766</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1939</v>
+        <v>-0.662</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0161</v>
+        <v>-0.0954</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7488</v>
+        <v>0.0047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2673</v>
+        <v>-0.1001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2071</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9224</v>
+        <v>-3.0746</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7519</v>
+        <v>-1.2458</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1705</v>
+        <v>-1.8288</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3896</v>
+        <v>-2.7723</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2092</v>
+        <v>-0.9739</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1804</v>
+        <v>-1.7984</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.451</v>
+        <v>-1.177</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0674</v>
+        <v>-0.5782</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5184</v>
+        <v>-0.5988</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9386</v>
+        <v>-1.5953</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2766</v>
+        <v>-0.3957</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.662</v>
+        <v>-1.1996</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3168</v>
+        <v>-0.2845</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.301</v>
+        <v>-0.0688</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0158</v>
+        <v>-0.2157</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2071</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4769</v>
+        <v>-3.2622</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6762</v>
+        <v>0.6681</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8007</v>
+        <v>-3.9303</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7723</v>
+        <v>-2.8407</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9739</v>
+        <v>-1.0498</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7984</v>
+        <v>-1.7909</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.177</v>
+        <v>0.3421</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5782</v>
+        <v>0.1412</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5988</v>
+        <v>0.2009</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5953</v>
+        <v>-3.1828</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3957</v>
+        <v>-1.191</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1996</v>
+        <v>-1.9918</v>
       </c>
       <c r="P13" t="n">
         <v>1.1893</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6868</v>
+        <v>-0.4038</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4992</v>
+        <v>0.5242</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1876</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.8779</v>
+        <v>-11.4008</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.847799999999999</v>
+        <v>-8.174200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.0301</v>
+        <v>-3.2267</v>
       </c>
       <c r="G14" t="n">
         <v>-6.1054</v>
@@ -1546,13 +1546,13 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3938</v>
+        <v>-0.9167</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3103</v>
+        <v>-0.6367</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0835</v>
+        <v>-0.28</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.8544</v>
+        <v>-19.9184</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.267799999999999</v>
+        <v>-0.331900000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.5868</v>
+        <v>-19.5867</v>
       </c>
       <c r="G15" t="n">
         <v>-15.8427</v>
@@ -1624,13 +1624,13 @@
         <v>16.8489</v>
       </c>
       <c r="S15" t="n">
-        <v>-6.148299999999999</v>
+        <v>-5.2123</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.4028</v>
+        <v>-1.4668</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.7455</v>
+        <v>-3.7456</v>
       </c>
       <c r="V15" t="n">
         <v>1.136599999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5155</v>
+        <v>8.235799999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>8.745900000000001</v>
+        <v>9.662699999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2304</v>
+        <v>-1.4269</v>
       </c>
       <c r="G16" t="n">
         <v>7.0473</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1862</v>
+        <v>0.5341</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4771</v>
+        <v>0.4397</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2909</v>
+        <v>0.0944</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3278</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.1558</v>
+        <v>5.0975</v>
       </c>
       <c r="E17" t="n">
-        <v>6.9589</v>
+        <v>5.1252</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1969</v>
+        <v>-0.0277</v>
       </c>
       <c r="G17" t="n">
         <v>0.3617</v>
@@ -1780,13 +1780,13 @@
         <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8992</v>
+        <v>1.8409</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1278</v>
+        <v>1.2941</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7714</v>
+        <v>0.5468</v>
       </c>
       <c r="V17" t="n">
         <v>3.0932</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7672</v>
+        <v>4.2648</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4435</v>
+        <v>3.7491</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3237</v>
+        <v>0.5157</v>
       </c>
       <c r="G18" t="n">
         <v>2.3804</v>
@@ -1858,13 +1858,13 @@
         <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1203</v>
+        <v>1.6178</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7564</v>
+        <v>1.062</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3639</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.2666</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6352</v>
+        <v>2.3988</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4572</v>
+        <v>0.2535</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1779</v>
+        <v>2.1453</v>
       </c>
       <c r="G19" t="n">
         <v>5.1227</v>
@@ -1936,13 +1936,13 @@
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5541</v>
+        <v>1.3178</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7343</v>
+        <v>0.5305</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8199</v>
+        <v>0.7872</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8701</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>N. KOROL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.287</v>
+        <v>2.2268</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3603</v>
+        <v>4.6522</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0733</v>
+        <v>-2.4254</v>
       </c>
       <c r="G20" t="n">
-        <v>4.0259</v>
+        <v>1.3347</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6044</v>
+        <v>1.1856</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4215</v>
+        <v>0.149</v>
       </c>
       <c r="J20" t="n">
-        <v>5.315</v>
+        <v>4.2423</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8525</v>
+        <v>2.1129</v>
       </c>
       <c r="L20" t="n">
-        <v>2.4625</v>
+        <v>2.1294</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2891</v>
+        <v>-2.9076</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2481</v>
+        <v>-0.9272</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.041</v>
+        <v>-1.9804</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.9556</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7751</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9764</v>
+        <v>0.6075</v>
       </c>
       <c r="T20" t="n">
-        <v>2.0008</v>
+        <v>0.3149</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0244</v>
+        <v>0.2926</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5349</v>
+        <v>0.4828</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5349</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. KOROL</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2819</v>
+        <v>1.6275</v>
       </c>
       <c r="E21" t="n">
-        <v>3.7354</v>
+        <v>-0.2772</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4535</v>
+        <v>1.9047</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3347</v>
+        <v>-0.2808</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1856</v>
+        <v>1.1215</v>
       </c>
       <c r="I21" t="n">
-        <v>0.149</v>
+        <v>-1.4023</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2423</v>
+        <v>-0.1681</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1129</v>
+        <v>1.1098</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1294</v>
+        <v>-1.2779</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9076</v>
+        <v>-0.1126</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9272</v>
+        <v>0.0118</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9804</v>
+        <v>-0.1244</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3374</v>
+        <v>-0.3515</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6019</v>
+        <v>-0.1091</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2645</v>
+        <v>-0.2423</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4828</v>
+        <v>0.674</v>
       </c>
       <c r="W21" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5944</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0973</v>
+        <v>0.3654</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5829</v>
+        <v>-0.0743</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6801</v>
+        <v>0.4397</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2808</v>
+        <v>0.3415</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1215</v>
+        <v>0.3415</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4023</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1681</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1098</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2779</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1126</v>
+        <v>0.3415</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0118</v>
+        <v>0.3415</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1244</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8817</v>
+        <v>-0.1744</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4147</v>
+        <v>-0.0743</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.467</v>
+        <v>-0.1001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3478</v>
+        <v>0.109</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1762</v>
+        <v>0.9341</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5239</v>
+        <v>-0.8252</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3415</v>
+        <v>4.0259</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3415</v>
+        <v>2.6044</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1.4215</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>5.315</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2.8525</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.4625</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3415</v>
+        <v>-1.2891</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3415</v>
+        <v>-0.2481</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-1.041</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-4.9556</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1982</v>
+        <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.192</v>
+        <v>0.7984</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1762</v>
+        <v>0.5747</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0158</v>
+        <v>0.2237</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.5349</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.5349</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2368</v>
+        <v>-0.2087</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1248</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.112</v>
+        <v>-0.0839</v>
       </c>
       <c r="G24" t="n">
         <v>0.2717</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2419</v>
+        <v>-0.2138</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2666</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3314</v>
+        <v>-0.3137</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.7534</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5239</v>
+        <v>0.4397</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3376</v>
@@ -2404,13 +2404,13 @@
         <v>0.1982</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.192</v>
+        <v>-0.1744</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1762</v>
+        <v>-0.0743</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0158</v>
+        <v>-0.1001</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.5341</v>
+        <v>-0.8328</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5238</v>
+        <v>-2.0145</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9897</v>
+        <v>1.1817</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2047</v>
@@ -2482,13 +2482,13 @@
         <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0667</v>
+        <v>0.7681</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4257</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4925</v>
+        <v>0.6845</v>
       </c>
       <c r="V26" t="n">
         <v>0.2163</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.131</v>
+        <v>-1.4368</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8516</v>
+        <v>-1.546</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2794</v>
+        <v>0.1092</v>
       </c>
       <c r="G27" t="n">
         <v>-1.2201</v>
@@ -2560,13 +2560,13 @@
         <v>1.3876</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.4372</v>
+        <v>0.2569</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4771</v>
+        <v>-0.1715</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0399</v>
+        <v>0.4284</v>
       </c>
       <c r="V27" t="n">
         <v>-0.8701</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>20.85440000000001</v>
+        <v>21.5336</v>
       </c>
       <c r="E28" t="n">
         <v>19.5866</v>
       </c>
       <c r="F28" t="n">
-        <v>1.267500000000001</v>
+        <v>1.946900000000001</v>
       </c>
       <c r="G28" t="n">
         <v>15.8427</v>
@@ -2638,13 +2638,13 @@
         <v>16.8489</v>
       </c>
       <c r="S28" t="n">
-        <v>6.1483</v>
+        <v>6.827399999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>3.7456</v>
+        <v>3.7455</v>
       </c>
       <c r="U28" t="n">
-        <v>2.4029</v>
+        <v>3.082</v>
       </c>
       <c r="V28" t="n">
         <v>-1.1366</v>
